--- a/Configs/GameConfig/Datas/ProfileConfig.xlsx
+++ b/Configs/GameConfig/Datas/ProfileConfig.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>StartGold</t>
+          <t>StartSoul</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>新档初始金币</t>
+          <t>初始灵魂</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/ProfileConfig.xlsx
+++ b/Configs/GameConfig/Datas/ProfileConfig.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6ae206b7e0e4517"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,12 +43,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -288,7 +283,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +292,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -337,17 +332,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -402,124 +386,128 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>StartHeroId</t>
+          <t xml:space="preserve">StartHeroId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>StartSoul</t>
-        </is>
+          <t xml:space="preserve">StartSoul</t>
+        </is>
+      </c>
+      <c r="F1" t="str">
+        <v>EquipmentCapacity</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
-        </is>
-      </c>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t xml:space="preserve">##type</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F3" t="str">
+        <v>int</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
+          <t xml:space="preserve">##group</t>
+        </is>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t xml:space="preserve">中文名</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t xml:space="preserve">描述</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新档的出战英雄(HeroConfig.Id)</t>
+          <t xml:space="preserve">新档的出战英雄(HeroConfig.Id)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初始灵魂</t>
-        </is>
+          <t xml:space="preserve">初始灵魂</t>
+        </is>
+      </c>
+      <c r="F5" t="str">
+        <v>装备背包容量，三页每页25格</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>建档规则</t>
+          <t xml:space="preserve">建档规则</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新建存档时的初始档案</t>
+          <t xml:space="preserve">新建存档时的初始档案</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -528,8 +516,11 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>